--- a/Result/checksun_type/冷凍、罐頭、脫水、醃漬食品.xlsx
+++ b/Result/checksun_type/冷凍、罐頭、脫水、醃漬食品.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>31.06</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>30.94</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>31.11</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>30.94</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>31.11</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>186.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>347.8</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>347.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>567.6</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>0</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-31.01728687031533</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>186</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>186.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>31.08</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>30.94</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>31.11</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>30.94</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>31.11</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>590.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>366.4</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>366.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>660.6</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>0</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-6.356760914500455</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>590</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>590.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>31.08</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>30.95</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>31.11</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>30.95</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>31.11</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>465.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>410.4</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>410.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>685.0</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>0</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-14.18612523067566</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>465</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>465.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>30.97</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>30.96</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>31.09</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>30.96</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>31.09</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>155.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>447.6</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>447.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>694.1</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>0</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-11.47142692411603</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>155</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>30.99</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>31.01</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>31.09</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>31.01</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>31.09</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>343.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>744.4</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>744.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>745.0</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>0</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>26.03069304683038</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>343</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>343.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>31.01</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>31.03</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>31.08</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>31.03</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>31.08</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>279.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>787.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>787.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>735.9</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>0</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>58.53262539650984</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>279</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>31.0</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>31.02</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>31.07</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>31.02</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>31.07</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>810.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>954.8</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>954.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>714.2</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>0</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>109.7306492747481</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>810</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>810.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>30.99</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>31.02</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>31.05</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>31.02</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>31.05</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>651.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>959.6</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>959.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>660.9</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>0</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>122.0588744838474</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>651</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>651.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>30.98</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>31.01</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>31.03</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>31.01</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>31.03</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>1639.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>940.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>940.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>617.6</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>0</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>152.3470935509947</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>1639</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>1639.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>30.98</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>31.0</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>31.01</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>31</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>31.01</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>558.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>745.6</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>745.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>494.1</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>0</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>84.31786744866986</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>558</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>558.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>30.9</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>30.99</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>31.0</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>30.99</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>31</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>1116.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>684.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>684.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>463.1</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>0</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>99.94333489361031</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>1116</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>1116.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>13.46</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>13.82</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>13.82</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>14</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>10142207.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>10933769.4</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>10933769.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>16296908.7</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>17901343.42</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>17901343.42</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-1502074.410510352</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>10142207</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>10142207.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>13.36</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>13.84</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>14.01</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>13.84</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>14.01</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>7913681.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>15352877.6</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>15352877.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>17879236.8</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>18605615.68</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>18605615.68</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-1271889.949924694</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>7913681</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>7913681.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>13.39</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>13.86</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>14.03</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>13.86</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>14.03</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>14384179.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>19283284.4</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>19283284.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>18214428.6</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>19000401.92</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>19000401.92</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-658859.7223050147</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>14384179</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>14384179.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>13.5</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>13.92</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>14.06</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>13.92</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>14.06</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>10460807.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>19640876.6</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>19640876.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>17805722.5</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>19007964.5</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>19007964.5</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-452839.1927660033</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>10460807</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>10460807.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>13.61</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>13.97</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>14.08</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>14.08</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>11767973.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>20788530.4</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>20788530.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>17800069.4</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>18961607.6</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>18961607.6</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>278009.9634599388</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>11767973</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>11767973.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>13.77</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>14.01</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>14.11</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>14.11</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>32237748.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>21660048.0</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>21660048</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>19618613.0</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>19128823.28</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>19128823.28</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>1172097.759373426</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>32237748</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>32237748.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>13.99</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>14.05</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>14.14</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>14.14</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>27565715.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>20405596.0</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>20405596</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>18100015.2</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>19224091.9</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>19224091.9</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>214315.2264150791</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>27565715</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>27565715.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>14.06</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>14.07</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>14.16</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>14.16</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>16172140.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>17145572.8</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>17145572.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>16576776.3</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>18869466.3</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>18869466.3</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-661024.6858973876</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>16172140</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>16172140.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>14.08</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>14.08</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>14.18</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>14.18</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>16199076.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>15970568.4</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>15970568.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>16162107.7</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>18784892.82</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>18784892.82</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-667162.0718474351</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>16199076</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>16199076.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>14.1</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>14.08</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>14.19</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>14.19</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>16125561.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>14811608.4</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>14811608.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>15973487.8</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>18696390.84</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>18696390.84</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-654988.5492100939</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>16125561</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>16125561.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>14.13</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>14.07</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>14.2</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>14.2</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>25965488.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>17577178.0</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>17577178</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>15340744.0</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>18728032.0</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>18728032</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-606328.747256387</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>25965488</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>25965488.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>37.7</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>37.34</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>37.75</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>37.34</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>37.75</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>2815644.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>3021205.2</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>3021205.2</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>3832148.1</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>4668867.04</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>4668867.04</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-449301.4540321333</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>2815644</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>2815644.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>37.52</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>37.31</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>37.76</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>37.31</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>37.76</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>1203852.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>3024985.6</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>3024985.6</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>3957083.9</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>4786918.46</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>4786918.46</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-457873.6219698172</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>1203852</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>1203852.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>37.41</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>37.3</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>37.8</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>37.8</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>2093649.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>3803968.6</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>3803968.6</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>4279460.1</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>4893132.92</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>4893132.92</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-281074.9468104439</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>2093649</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>2093649.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>37.36</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>37.3</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>37.83</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>37.83</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>5047539.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>4198523.2</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>4198523.2</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>4848042.1</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>5002879.18</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>5002879.18</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-113802.4127681088</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>5047539</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>5047539.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>37.32000000000001</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>37.3</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>37.87</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>37.87</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>3945342.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>3868059.2</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>3868059.2</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>4688050.3</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>4943301.7</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>4943301.7</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-187265.4922516262</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>3945342</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>3945342.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>37.26</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>37.3</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>37.9</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>37.9</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>2834546.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>4643091.0</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>4643091</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>4661301.7</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>4893190.98</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>4893190.98</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-167432.159647665</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>2834546</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>2834546.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>37.35</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>37.33</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>37.95</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>37.33</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>37.95</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>5098767.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>4889182.2</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>4889182.2</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>5012955.6</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>4919509.2</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>4919509.2</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-14105.25022601709</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>5098767</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>5098767.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>37.37</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>37.34</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>37.99</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>37.34</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>37.99</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>4066422.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>4754951.6</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>4754951.6</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>5037049.1</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>4842832.18</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>4842832.18</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-37158.15640130639</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>4066422</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>4066422.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>37.25</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>37.35</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>38.02</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>37.35</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>38.02</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>3395219.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>5497561.0</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>5497561</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>5136092.7</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>4841977.64</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>4841977.64</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>41844.59036261309</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>3395219</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>3395219.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>37.23999999999999</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>37.37</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>38.06</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>37.37</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>38.06</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>7820501.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>5508041.4</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>5508041.4</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>5324361.4</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>4840880.92</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>4840880.92</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>225125.814655263</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>7820501</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>7820501.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>37.19</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>37.39</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>38.1</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>37.39</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>38.1</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>4065002.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>4679512.4</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>4679512.4</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>5199521.0</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>4722502.12</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>4722502.12</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>4778.570264216512</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>4065002</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>4065002.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>97.47999999999999</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>101.46</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>113.73</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>101.46</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>113.73</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>51517147.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>35254204.2</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>35254204.2</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>66942362.9</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>55389338.24</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>55389338.24</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-5810146.594499774</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>51517147</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>51517147.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>95.92</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>102.06</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>114.37</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>102.06</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>114.37</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>28252495.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>30612578.0</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>30612578</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>73954054.3</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>55160480.98</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>55160480.98</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-6602595.717565864</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>28252495</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>28252495.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>95.12</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>102.82</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>115.09</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>102.82</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>115.09</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>38925498.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>39037504.6</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>39037504.6</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>88947777.6</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>55726460.0</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>55726460</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-5006217.61774721</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>38925498</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>38925498.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>95.26</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>103.61</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>115.84</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>103.61</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>115.84</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>30055449.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>47887835.6</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>47887835.6</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>94683268.3</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>55381472.96</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>55381472.96</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-3690420.024515301</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>30055449</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>30055449.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>94.96000000000001</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>104.39</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>116.62</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>104.39</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>116.62</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>27520432.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>62681929.0</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>62681929</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>93096070.7</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>55333080.92</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>55333080.92</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-728546.0690227449</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>27520432</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>27520432.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>94.72</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>105.24</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>117.44</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>105.24</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>117.44</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>28309016.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>98630521.6</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>98630521.59999999</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>91979313.7</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>55459640.54</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>55459640.54</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>3800330.90557456</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>28309016</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>28309016.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>95.8</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>106.13</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>118.33</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>106.13</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>118.33</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>70377128.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>117295530.6</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>117295530.6</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>92352695.6</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>55223649.66</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>55223649.66</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>10049937.90837163</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>70377128</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>70377128.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>96.94</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>107.08</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>119.18</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>107.08</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>119.18</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>83177153.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>138858050.6</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>138858050.6</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>88080304.9</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>54355564.16</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>54355564.16</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>14111723.84421133</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>83177153</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>83177153.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>98.08</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>108.0</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>120.0</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>108</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>120</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>104025916.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>141478701.0</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>141478701</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>86572166.3</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>53746000.08</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>53746000.08</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>18038853.79383193</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>104025916</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>104025916.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>100.8</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>108.9</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>120.79</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>120.79</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>207263395.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>123510212.4</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>123510212.4</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>78443474.3</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>52325803.62</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>52325803.62</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>20770998.62208164</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>207263395</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>207263395.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>103.94</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>109.88</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>121.64</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>109.88</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>121.64</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>121634061.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>85328105.8</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>85328105.8</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>62028058.2</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>48583744.56</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>48583744.56</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>12871082.8187926</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>121634061</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>121634061.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>18.09</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>18.24</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>18.69</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>18.24</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>18.69</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>6331649.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>5939688.0</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>5939688</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>9211411.4</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>15560196.66</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>15560196.66</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-1598233.966819468</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>6331649</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>6331649.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>18.03</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>18.25</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>18.71</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>18.71</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>3361074.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>6979571.0</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>6979571</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>9308848.0</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>16771300.44</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>16771300.44</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-1677226.086855883</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>3361074</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>3361074.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>18.02</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>18.28</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>18.72</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>18.28</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>18.72</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>3542147.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>9725469.8</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>9725469.800000001</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>10271216.4</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>16905496.38</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>16905496.38</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-1411895.148091624</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>3542147</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>3542147.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>18.04</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>18.3</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>18.74</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>18.74</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>10568715.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>11621647.4</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>11621647.4</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>10493231.5</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>17027313.68</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>17027313.68</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-1001826.801710838</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>10568715</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>10568715.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>18.14</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>18.34</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>18.76</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>18.34</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>18.76</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>5894855.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>10627198.6</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>10627198.6</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>10015643.0</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>17012149.28</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>17012149.28</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-1133081.921105757</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>5894855</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>5894855.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>18.22</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>18.38</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>18.77</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>18.77</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>11531064.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>12483134.8</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>12483134.8</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>10020343.9</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>17019203.88</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>17019203.88</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-779351.3087732922</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>11531064</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>11531064.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>18.3</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>18.42</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>18.79</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>18.42</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>18.79</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>17090568.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>11638125.0</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>11638125</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>9994190.0</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>16974224.12</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>16974224.12</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-850067.4229850136</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>17090568</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>17090568.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>18.32</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>18.45</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>18.8</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>18.45</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>18.8</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>13023035.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>10816963.0</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>10816963</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>9291956.6</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>16727953.58</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>16727953.58</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-1516392.03532372</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>13023035</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>13023035.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>18.32</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>18.49</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>18.81</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>18.49</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>18.81</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>5596471.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>9364815.6</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>9364815.6</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>9601148.6</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>16601609.44</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>16601609.44</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-1978320.373117454</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>5596471</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>5596471.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,21 +23847,17 @@
           <t>18.28</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>18.52</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
+      <c r="AM55" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>18.82</v>
+      </c>
+      <c r="AO55" t="inlineStr">
         <is>
           <t>18.82</t>
         </is>
       </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>18.82</t>
-        </is>
-      </c>
       <c r="AP55" t="inlineStr">
         <is>
           <t>-2.71</t>
@@ -24220,20 +23898,16 @@
           <t>15174536.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>9404087.4</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>9404087.4</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>10136777.1</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>16601544.8</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>16601544.8</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-1771860.413782878</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>15174536</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>15174536.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>18.26</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>18.58</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>18.82</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>18.58</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>18.82</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>7306015.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>7557553.0</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>7557553</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>10438231.1</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>16403922.6</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>16403922.6</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-2439858.135669811</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>7306015</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>7306015.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>10.27</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>10.24</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>10.4</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>10.4</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>5707727.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>4196773.0</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>4196773</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>4496203.2</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>4907615.04</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>4907615.04</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-3245.902898706496</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>5707727</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>5707727.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>10.2</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>10.23</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>10.4</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>10.4</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>2795948.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>4037496.4</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>4037496.4</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>4176139.8</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>4976588.2</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>4976588.2</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-137656.2918490865</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>2795948</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>2795948.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>10.18</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>10.24</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>10.42</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>10.42</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>5692248.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>4199415.2</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>4199415.2</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>4239605.4</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>5085447.66</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>5085447.66</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-12778.51564073376</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>5692248</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>5692248.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>10.18</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>10.25</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>10.43</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>10.43</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>4051171.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>4121962.6</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>4121962.6</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>4208580.9</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>5077815.48</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>5077815.48</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-144243.1740702032</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>4051171</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>4051171.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>10.18</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>10.26</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>10.45</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>10.45</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>2736771.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>4758195.2</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>4758195.2</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>4173883.9</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>5092414.34</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>5092414.34</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-151068.6084669381</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>2736771</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>2736771.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>10.19</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>10.27</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>10.46</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>10.27</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>10.46</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>4911344.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>4795633.4</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>4795633.4</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>4280369.3</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>5142239.04</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>5142239.04</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>-14595.35015988257</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>4911344</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>4911344.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>10.22</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>10.28</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>10.48</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>10.48</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>3605542.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>4314783.2</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>4314783.2</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>4501155.2</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>5200069.92</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>5200069.92</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>-52102.25435837824</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>3605542</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>3605542.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>10.22</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>10.5</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>5304985.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>4279795.6</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>4279795.6</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>4854338.3</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>5233210.08</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>5233210.08</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>36084.60587085504</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>5304985</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>5304985.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>10.19</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>10.51</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>10.51</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>7232334.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>4295199.2</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>4295199.2</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>4765788.7</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>5228733.88</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>5228733.88</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-21306.07972562779</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>7232334</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>7232334.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>10.2</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>10.31</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>10.53</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>10.53</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>2923962.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>3589572.6</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>3589572.6</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>4335716.6</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>5274598.0</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>5274598</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-309033.5205875444</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>2923962</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>2923962.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>10.22</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>10.31</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>10.54</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>10.54</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>2507093.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>3765105.2</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>3765105.2</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>4545765.6</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>5558067.66</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>5558067.66</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>-247424.5246550129</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>2507093</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>2507093.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>74.96000000000001</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>76.1</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>77.55</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>77.55</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>580572021.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>761372434.4</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>761372434.4</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>713281953.2</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>591852182.46</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>591852182.46</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>20200160.18291521</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>580572021</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>580572021.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>74.88</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>76.28</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>77.62</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>76.28</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>77.62</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>567170176.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>759956482.4</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>759956482.4</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>715597438.6</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>592899846.08</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>592899846.08</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>37783327.83082056</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>567170176</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>567170176.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>74.9</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>76.48</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>77.71</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>76.48</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>77.70999999999999</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>1247043677.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>796813281.6</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>796813281.6</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>764355055.9</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>596823360.36</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>596823360.36</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>62988646.15529895</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>1247043677</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>1247043677.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>74.93999999999998</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>76.69</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>77.8</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>76.69</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>77.8</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>930432408.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>670962016.2</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>670962016.2</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>719097614.7</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>590012176.16</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>590012176.16</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>23903059.86329317</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>930432408</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>930432408.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>75.02000000000001</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>76.95</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>77.89</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>76.95</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>77.89</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>481643890.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>588803301.8</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>588803301.8</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>707272105.3</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>582215741.78</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>582215741.78</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>1135463.27245307</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>481643890</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>481643890.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>74.98</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>77.14</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>77.95</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>77.14</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>77.95</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>573492261.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>665191472.0</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>665191472</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>712646224.7</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>580329214.24</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>580329214.24</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>16654257.09723663</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>573492261</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>573492261.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>75.08</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>77.36</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>78.01</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>77.36</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>78.01000000000001</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>751454172.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>671238394.8</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>671238394.8</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>711163123.1</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>577360400.24</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>577360400.24</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>28388270.77202618</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>751454172</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>751454172.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>75.08</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>77.54</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>78.07</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>77.54000000000001</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>78.06999999999999</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>617787350.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>731896830.2</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>731896830.2</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>680237061.0</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>569229272.66</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>569229272.66</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>25069933.02986753</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>617787350</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>617787350.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>75.16</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>77.69</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>78.13</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>77.69</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>78.13</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>519638836.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>767233213.2</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>767233213.2</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>657550176.6</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>565262583.96</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>565262583.96</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>33755541.00428843</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>519638836</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>519638836.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>75.4</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>77.82</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>78.18</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>77.81999999999999</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>78.18000000000001</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>863584741.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>825740908.8</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>825740908.8</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>656886555.4</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>560988698.04</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>560988698.04</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>55473909.57473648</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>863584741</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>863584741.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>75.94000000000001</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>77.95</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>78.23</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>77.95</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>78.23</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>603726875.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>760100977.4</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>760100977.4</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>620276259.3</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>561962584.56</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>561962584.5599999</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>47667592.36913598</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>603726875</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>603726875.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33983,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34167,11 @@
           <t>138.7</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>137.75</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>137.22</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>137.75</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>137.22</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34218,16 @@
           <t>413662509.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>183789694.6</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>183789694.6</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>172582561.6</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>199637575.92</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>199637575.92</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34244,10 @@
           <t>5866106.705132216</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>413662509</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>413662509.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34597,11 @@
           <t>136.6</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>137.38</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>137.05</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>137.38</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>137.05</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34648,16 @@
           <t>187766458.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>138477340.0</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>138477340</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>151909159.2</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>193347224.48</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>193347224.48</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34674,10 @@
           <t>-16034004.2940799</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>187766458</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>187766458.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34843,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35027,11 @@
           <t>135.8</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>137.25</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>137.0</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>137.25</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>137</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35078,16 @@
           <t>113957261.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>125349182.0</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>125349182</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>145142496.9</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>192518241.68</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>192518241.68</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35104,10 @@
           <t>-22544085.81816572</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>113957261</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>113957261.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35273,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35457,11 @@
           <t>135.4</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>137.43</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>136.98</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>137.43</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>136.98</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35508,16 @@
           <t>81205434.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>132206148.0</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>132206148</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>154603493.0</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>191830890.34</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>191830890.34</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35534,10 @@
           <t>-23130928.10906813</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>81205434</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>81205434.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35703,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35887,11 @@
           <t>135.7</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>137.32</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>136.96</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>137.32</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>136.96</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35938,16 @@
           <t>122356811.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>149577634.0</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>149577634</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>159565425.1</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>193010895.18</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>193010895.18</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35964,10 @@
           <t>-19634045.34217629</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>122356811</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>122356811.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36317,11 @@
           <t>135.5</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>137.35</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>136.88</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>137.35</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>136.88</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36368,16 @@
           <t>187100736.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>161375428.6</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>161375428.6</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>157437273.9</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>191546571.58</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>191546571.58</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36394,10 @@
           <t>-18346358.73439592</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>187100736</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>187100736.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36563,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36747,11 @@
           <t>136.4</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>137.4</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>136.87</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>137.4</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>136.87</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36798,16 @@
           <t>122125668.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>165340978.4</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>165340978.4</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>149108243.9</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>188946749.44</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>188946749.44</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36824,10 @@
           <t>-22788428.44705272</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>122125668</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>122125668.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36993,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37177,11 @@
           <t>136.4</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>137.43</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>136.85</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>137.43</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>136.85</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37228,16 @@
           <t>148242091.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>164935811.8</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>164935811.8</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>166343613.0</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>187261684.44</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>187261684.44</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37254,10 @@
           <t>-21358755.44916764</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>148242091</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>148242091.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37423,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37607,11 @@
           <t>136.8</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>138.0</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>136.84</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>138</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>136.84</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37658,16 @@
           <t>168062864.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>177000838.0</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>177000838</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>162923184.7</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>184983524.96</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>184983524.96</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37684,10 @@
           <t>-21351740.93614727</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>168062864</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>168062864.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37853,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38037,11 @@
           <t>137.2</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>138.15</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>136.75</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>138.15</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>136.75</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38088,16 @@
           <t>181345784.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>169553216.2</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>169553216.2</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>156579849.0</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>182347067.96</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>182347067.96</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38114,10 @@
           <t>-22702812.27697009</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>181345784</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>181345784.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38283,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38467,11 @@
           <t>138.3</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>138.32</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>136.71</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>138.32</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>136.71</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38518,16 @@
           <t>206928485.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>153499119.2</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>153499119.2</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>151300622.8</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>179584109.7</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>179584109.7</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38544,10 @@
           <t>-25245269.46825373</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>206928485</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>206928485.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
@@ -39241,7 +38713,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -39425,15 +38897,11 @@
           <t>51.67999999999999</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>52.46</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>52.36</t>
-        </is>
+      <c r="AM90" t="n">
+        <v>52.46</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>52.36</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -39480,20 +38948,16 @@
           <t>57624928.0</t>
         </is>
       </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>58721264.4</t>
-        </is>
+      <c r="AX90" t="n">
+        <v>58721264.4</v>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>77833246.8</t>
         </is>
       </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>169895575.14</t>
-        </is>
+      <c r="AZ90" t="n">
+        <v>169895575.14</v>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
@@ -39510,8 +38974,10 @@
           <t>-25801342.54792771</t>
         </is>
       </c>
-      <c r="BD90" t="n">
-        <v>57624928</v>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>57624928.0</t>
+        </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
@@ -39677,7 +39143,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39861,15 +39327,11 @@
           <t>51.42</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>52.46</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>52.37</t>
-        </is>
+      <c r="AM91" t="n">
+        <v>52.46</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>52.37</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -39916,20 +39378,16 @@
           <t>36424814.0</t>
         </is>
       </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>77028734.2</t>
-        </is>
+      <c r="AX91" t="n">
+        <v>77028734.2</v>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
           <t>81701780.4</t>
         </is>
       </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>170050991.26</t>
-        </is>
+      <c r="AZ91" t="n">
+        <v>170050991.26</v>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
@@ -39946,8 +39404,10 @@
           <t>-27342195.96343875</t>
         </is>
       </c>
-      <c r="BD91" t="n">
-        <v>36424814</v>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>36424814.0</t>
+        </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
@@ -40113,7 +39573,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -40297,15 +39757,11 @@
           <t>51.42</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>52.52</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>52.4</t>
-        </is>
+      <c r="AM92" t="n">
+        <v>52.52</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>52.4</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -40352,20 +39808,16 @@
           <t>58969633.0</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>96496985.2</t>
-        </is>
+      <c r="AX92" t="n">
+        <v>96496985.2</v>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
           <t>85858420.7</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>170916126.08</t>
-        </is>
+      <c r="AZ92" t="n">
+        <v>170916126.08</v>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
@@ -40382,8 +39834,10 @@
           <t>-26295467.344046</t>
         </is>
       </c>
-      <c r="BD92" t="n">
-        <v>58969633</v>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>58969633.0</t>
+        </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
@@ -40549,7 +40003,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40733,15 +40187,11 @@
           <t>51.6</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>52.69</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>52.44</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>52.69</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>52.44</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -40788,20 +40238,16 @@
           <t>83783480.0</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>100418492.2</t>
-        </is>
+      <c r="AX93" t="n">
+        <v>100418492.2</v>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
           <t>92360024.3</t>
         </is>
       </c>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>170656127.5</t>
-        </is>
+      <c r="AZ93" t="n">
+        <v>170656127.5</v>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
@@ -40818,8 +40264,10 @@
           <t>-26276533.23262614</t>
         </is>
       </c>
-      <c r="BD93" t="n">
-        <v>83783480</v>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>83783480.0</t>
+        </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
@@ -40985,7 +40433,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -41169,15 +40617,11 @@
           <t>51.88000000000001</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>52.85</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>52.48</t>
-        </is>
+      <c r="AM94" t="n">
+        <v>52.85</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>52.48</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -41224,20 +40668,16 @@
           <t>56803467.0</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>95072697.2</t>
-        </is>
+      <c r="AX94" t="n">
+        <v>95072697.2</v>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
           <t>92841295.7</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>169926457.4</t>
-        </is>
+      <c r="AZ94" t="n">
+        <v>169926457.4</v>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
@@ -41254,8 +40694,10 @@
           <t>-27969663.35086113</t>
         </is>
       </c>
-      <c r="BD94" t="n">
-        <v>56803467</v>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>56803467.0</t>
+        </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
@@ -41421,7 +40863,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -41605,15 +41047,11 @@
           <t>52.08</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>53.04</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>52.51</t>
-        </is>
+      <c r="AM95" t="n">
+        <v>53.04</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>52.51</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -41660,20 +41098,16 @@
           <t>149162277.0</t>
         </is>
       </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>96945229.2</t>
-        </is>
+      <c r="AX95" t="n">
+        <v>96945229.2</v>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
           <t>97295772.0</t>
         </is>
       </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>169884277.64</t>
-        </is>
+      <c r="AZ95" t="n">
+        <v>169884277.64</v>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
@@ -41690,8 +41124,10 @@
           <t>-26498788.43580891</t>
         </is>
       </c>
-      <c r="BD95" t="n">
-        <v>149162277</v>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>149162277.0</t>
+        </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
@@ -41857,7 +41293,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -42041,15 +41477,11 @@
           <t>52.54</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>53.06</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>52.56</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>53.06</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>52.56</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -42096,20 +41528,16 @@
           <t>133766069.0</t>
         </is>
       </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>86374826.6</t>
-        </is>
+      <c r="AX96" t="n">
+        <v>86374826.59999999</v>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
           <t>92435363.1</t>
         </is>
       </c>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>167512996.52</t>
-        </is>
+      <c r="AZ96" t="n">
+        <v>167512996.52</v>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
@@ -42126,8 +41554,10 @@
           <t>-33346740.04159831</t>
         </is>
       </c>
-      <c r="BD96" t="n">
-        <v>133766069</v>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>133766069.0</t>
+        </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
@@ -42293,7 +41723,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -42477,15 +41907,11 @@
           <t>52.73999999999999</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>53.05</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>52.59</t>
-        </is>
+      <c r="AM97" t="n">
+        <v>53.05</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>52.59</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -42532,20 +41958,16 @@
           <t>78577168.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>75219856.2</t>
-        </is>
+      <c r="AX97" t="n">
+        <v>75219856.2</v>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
           <t>96360927.8</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>166307928.74</t>
-        </is>
+      <c r="AZ97" t="n">
+        <v>166307928.74</v>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
@@ -42562,8 +41984,10 @@
           <t>-40288979.33409747</t>
         </is>
       </c>
-      <c r="BD97" t="n">
-        <v>78577168</v>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>78577168.0</t>
+        </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
@@ -42729,7 +42153,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -42913,15 +42337,11 @@
           <t>52.86</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>53.01</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>52.61</t>
-        </is>
+      <c r="AM98" t="n">
+        <v>53.01</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>52.61</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -42968,20 +42388,16 @@
           <t>57054505.0</t>
         </is>
       </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>84301556.4</t>
-        </is>
+      <c r="AX98" t="n">
+        <v>84301556.40000001</v>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
           <t>101068862.5</t>
         </is>
       </c>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>165959261.12</t>
-        </is>
+      <c r="AZ98" t="n">
+        <v>165959261.12</v>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
@@ -42998,8 +42414,10 @@
           <t>-42854475.38287853</t>
         </is>
       </c>
-      <c r="BD98" t="n">
-        <v>57054505</v>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>57054505.0</t>
+        </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
@@ -43165,7 +42583,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -43349,15 +42767,11 @@
           <t>53.1</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>52.96</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>52.62</t>
-        </is>
+      <c r="AM99" t="n">
+        <v>52.96</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>52.62</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -43404,20 +42818,16 @@
           <t>66166127.0</t>
         </is>
       </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>90609894.2</t>
-        </is>
+      <c r="AX99" t="n">
+        <v>90609894.2</v>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
           <t>106180540.0</t>
         </is>
       </c>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>165905598.5</t>
-        </is>
+      <c r="AZ99" t="n">
+        <v>165905598.5</v>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
@@ -43434,8 +42844,10 @@
           <t>-42682953.15317722</t>
         </is>
       </c>
-      <c r="BD99" t="n">
-        <v>66166127</v>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>66166127.0</t>
+        </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
@@ -43601,7 +43013,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -43785,15 +43197,11 @@
           <t>53.3</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>52.94</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>52.63</t>
-        </is>
+      <c r="AM100" t="n">
+        <v>52.94</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>52.63</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -43840,20 +43248,16 @@
           <t>96310264.0</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>97646314.8</t>
-        </is>
+      <c r="AX100" t="n">
+        <v>97646314.8</v>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
           <t>114316438.0</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>166957387.08</t>
-        </is>
+      <c r="AZ100" t="n">
+        <v>166957387.08</v>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
@@ -43870,8 +43274,10 @@
           <t>-41889775.42670473</t>
         </is>
       </c>
-      <c r="BD100" t="n">
-        <v>96310264</v>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>96310264.0</t>
+        </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
@@ -44037,7 +43443,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -44221,15 +43627,11 @@
           <t>39.73</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>39.56</t>
-        </is>
-      </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>39.6</t>
-        </is>
+      <c r="AM101" t="n">
+        <v>39.56</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>39.6</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
@@ -44276,20 +43678,16 @@
           <t>322098.0</t>
         </is>
       </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>445197.8</t>
-        </is>
+      <c r="AX101" t="n">
+        <v>445197.8</v>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
           <t>607508.9</t>
         </is>
       </c>
-      <c r="AZ101" t="inlineStr">
-        <is>
-          <t>769654.62</t>
-        </is>
+      <c r="AZ101" t="n">
+        <v>769654.62</v>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
@@ -44306,8 +43704,10 @@
           <t>-74779.86981358624</t>
         </is>
       </c>
-      <c r="BD101" t="n">
-        <v>322098</v>
+      <c r="BD101" t="inlineStr">
+        <is>
+          <t>322098.0</t>
+        </is>
       </c>
       <c r="BE101" t="inlineStr">
         <is>
@@ -44473,7 +43873,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -44657,15 +44057,11 @@
           <t>39.67</t>
         </is>
       </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>39.56</t>
-        </is>
-      </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>39.6</t>
-        </is>
+      <c r="AM102" t="n">
+        <v>39.56</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>39.6</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
@@ -44712,20 +44108,16 @@
           <t>160690.0</t>
         </is>
       </c>
-      <c r="AX102" t="inlineStr">
-        <is>
-          <t>431706.0</t>
-        </is>
+      <c r="AX102" t="n">
+        <v>431706</v>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
           <t>725648.6</t>
         </is>
       </c>
-      <c r="AZ102" t="inlineStr">
-        <is>
-          <t>791157.88</t>
-        </is>
+      <c r="AZ102" t="n">
+        <v>791157.88</v>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
@@ -44742,8 +44134,10 @@
           <t>-65950.38123613526</t>
         </is>
       </c>
-      <c r="BD102" t="n">
-        <v>160690</v>
+      <c r="BD102" t="inlineStr">
+        <is>
+          <t>160690.0</t>
+        </is>
       </c>
       <c r="BE102" t="inlineStr">
         <is>
@@ -44909,7 +44303,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -45093,15 +44487,11 @@
           <t>39.63</t>
         </is>
       </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>39.55</t>
-        </is>
-      </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>39.6</t>
-        </is>
+      <c r="AM103" t="n">
+        <v>39.55</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>39.6</v>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
@@ -45148,20 +44538,16 @@
           <t>573053.0</t>
         </is>
       </c>
-      <c r="AX103" t="inlineStr">
-        <is>
-          <t>598039.8</t>
-        </is>
+      <c r="AX103" t="n">
+        <v>598039.8</v>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
           <t>726953.7</t>
         </is>
       </c>
-      <c r="AZ103" t="inlineStr">
-        <is>
-          <t>792650.3</t>
-        </is>
+      <c r="AZ103" t="n">
+        <v>792650.3</v>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
@@ -45178,8 +44564,10 @@
           <t>-33687.74108134338</t>
         </is>
       </c>
-      <c r="BD103" t="n">
-        <v>573053</v>
+      <c r="BD103" t="inlineStr">
+        <is>
+          <t>573053.0</t>
+        </is>
       </c>
       <c r="BE103" t="inlineStr">
         <is>
@@ -45345,7 +44733,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -45529,15 +44917,11 @@
           <t>39.64</t>
         </is>
       </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>39.55</t>
-        </is>
-      </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>39.6</t>
-        </is>
+      <c r="AM104" t="n">
+        <v>39.55</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>39.6</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
@@ -45584,20 +44968,16 @@
           <t>438801.0</t>
         </is>
       </c>
-      <c r="AX104" t="inlineStr">
-        <is>
-          <t>661775.4</t>
-        </is>
+      <c r="AX104" t="n">
+        <v>661775.4</v>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
           <t>694473.5</t>
         </is>
       </c>
-      <c r="AZ104" t="inlineStr">
-        <is>
-          <t>791778.08</t>
-        </is>
+      <c r="AZ104" t="n">
+        <v>791778.08</v>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
@@ -45614,8 +44994,10 @@
           <t>-30576.87153587828</t>
         </is>
       </c>
-      <c r="BD104" t="n">
-        <v>438801</v>
+      <c r="BD104" t="inlineStr">
+        <is>
+          <t>438801.0</t>
+        </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
@@ -45781,7 +45163,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -45965,15 +45347,11 @@
           <t>39.56</t>
         </is>
       </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>39.53</t>
-        </is>
-      </c>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>39.6</t>
-        </is>
+      <c r="AM105" t="n">
+        <v>39.53</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>39.6</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
@@ -46020,20 +45398,16 @@
           <t>731347.0</t>
         </is>
       </c>
-      <c r="AX105" t="inlineStr">
-        <is>
-          <t>616178.6</t>
-        </is>
+      <c r="AX105" t="n">
+        <v>616178.6</v>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
           <t>711136.5</t>
         </is>
       </c>
-      <c r="AZ105" t="inlineStr">
-        <is>
-          <t>796845.52</t>
-        </is>
+      <c r="AZ105" t="n">
+        <v>796845.52</v>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
@@ -46050,8 +45424,10 @@
           <t>-10656.59820178954</t>
         </is>
       </c>
-      <c r="BD105" t="n">
-        <v>731347</v>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>731347.0</t>
+        </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
@@ -46217,7 +45593,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -46401,15 +45777,11 @@
           <t>39.55</t>
         </is>
       </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>39.54</t>
-        </is>
-      </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>39.6</t>
-        </is>
+      <c r="AM106" t="n">
+        <v>39.54</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>39.6</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
@@ -46456,20 +45828,16 @@
           <t>254639.0</t>
         </is>
       </c>
-      <c r="AX106" t="inlineStr">
-        <is>
-          <t>769820.0</t>
-        </is>
+      <c r="AX106" t="n">
+        <v>769820</v>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
           <t>723966.3</t>
         </is>
       </c>
-      <c r="AZ106" t="inlineStr">
-        <is>
-          <t>799138.1</t>
-        </is>
+      <c r="AZ106" t="n">
+        <v>799138.1</v>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
@@ -46486,8 +45854,10 @@
           <t>-13162.68636017037</t>
         </is>
       </c>
-      <c r="BD106" t="n">
-        <v>254639</v>
+      <c r="BD106" t="inlineStr">
+        <is>
+          <t>254639.0</t>
+        </is>
       </c>
       <c r="BE106" t="inlineStr">
         <is>
@@ -46653,7 +46023,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -46837,15 +46207,11 @@
           <t>39.59</t>
         </is>
       </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>39.55</t>
-        </is>
-      </c>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>39.61</t>
-        </is>
+      <c r="AM107" t="n">
+        <v>39.55</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>39.61</v>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
@@ -46892,20 +46258,16 @@
           <t>992359.0</t>
         </is>
       </c>
-      <c r="AX107" t="inlineStr">
-        <is>
-          <t>1019591.2</t>
-        </is>
+      <c r="AX107" t="n">
+        <v>1019591.2</v>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
           <t>811088.3</t>
         </is>
       </c>
-      <c r="AZ107" t="inlineStr">
-        <is>
-          <t>824802.82</t>
-        </is>
+      <c r="AZ107" t="n">
+        <v>824802.8199999999</v>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
@@ -46922,8 +46284,10 @@
           <t>34803.14078357734</t>
         </is>
       </c>
-      <c r="BD107" t="n">
-        <v>992359</v>
+      <c r="BD107" t="inlineStr">
+        <is>
+          <t>992359.0</t>
+        </is>
       </c>
       <c r="BE107" t="inlineStr">
         <is>
@@ -47089,7 +46453,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -47273,15 +46637,11 @@
           <t>39.56</t>
         </is>
       </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>39.56</t>
-        </is>
-      </c>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>39.63</t>
-        </is>
+      <c r="AM108" t="n">
+        <v>39.56</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>39.63</v>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
@@ -47328,20 +46688,16 @@
           <t>891731.0</t>
         </is>
       </c>
-      <c r="AX108" t="inlineStr">
-        <is>
-          <t>855867.6</t>
-        </is>
+      <c r="AX108" t="n">
+        <v>855867.6</v>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
           <t>829256.0</t>
         </is>
       </c>
-      <c r="AZ108" t="inlineStr">
-        <is>
-          <t>855051.52</t>
-        </is>
+      <c r="AZ108" t="n">
+        <v>855051.52</v>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
@@ -47358,8 +46714,10 @@
           <t>23041.35310380347</t>
         </is>
       </c>
-      <c r="BD108" t="n">
-        <v>891731</v>
+      <c r="BD108" t="inlineStr">
+        <is>
+          <t>891731.0</t>
+        </is>
       </c>
       <c r="BE108" t="inlineStr">
         <is>
@@ -47525,7 +46883,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -47709,15 +47067,11 @@
           <t>39.5</t>
         </is>
       </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>39.55</t>
-        </is>
-      </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>39.64</t>
-        </is>
+      <c r="AM109" t="n">
+        <v>39.55</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>39.64</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
@@ -47764,20 +47118,16 @@
           <t>210817.0</t>
         </is>
       </c>
-      <c r="AX109" t="inlineStr">
-        <is>
-          <t>727171.6</t>
-        </is>
+      <c r="AX109" t="n">
+        <v>727171.6</v>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
           <t>831126.9</t>
         </is>
       </c>
-      <c r="AZ109" t="inlineStr">
-        <is>
-          <t>841689.7</t>
-        </is>
+      <c r="AZ109" t="n">
+        <v>841689.7</v>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
@@ -47794,8 +47144,10 @@
           <t>16197.46523613355</t>
         </is>
       </c>
-      <c r="BD109" t="n">
-        <v>210817</v>
+      <c r="BD109" t="inlineStr">
+        <is>
+          <t>210817.0</t>
+        </is>
       </c>
       <c r="BE109" t="inlineStr">
         <is>
@@ -47961,7 +47313,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -48145,15 +47497,11 @@
           <t>39.5</t>
         </is>
       </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>39.58</t>
-        </is>
-      </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>39.64</t>
-        </is>
+      <c r="AM110" t="n">
+        <v>39.58</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>39.64</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
@@ -48200,20 +47548,16 @@
           <t>1499554.0</t>
         </is>
       </c>
-      <c r="AX110" t="inlineStr">
-        <is>
-          <t>806094.4</t>
-        </is>
+      <c r="AX110" t="n">
+        <v>806094.4</v>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
           <t>930594.4</t>
         </is>
       </c>
-      <c r="AZ110" t="inlineStr">
-        <is>
-          <t>862364.3</t>
-        </is>
+      <c r="AZ110" t="n">
+        <v>862364.3</v>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
@@ -48230,8 +47574,10 @@
           <t>78797.07309531455</t>
         </is>
       </c>
-      <c r="BD110" t="n">
-        <v>1499554</v>
+      <c r="BD110" t="inlineStr">
+        <is>
+          <t>1499554.0</t>
+        </is>
       </c>
       <c r="BE110" t="inlineStr">
         <is>
@@ -48397,7 +47743,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -48581,15 +47927,11 @@
           <t>39.5</t>
         </is>
       </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>39.56</t>
-        </is>
-      </c>
-      <c r="AN111" t="inlineStr">
-        <is>
-          <t>39.64</t>
-        </is>
+      <c r="AM111" t="n">
+        <v>39.56</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>39.64</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
@@ -48636,20 +47978,16 @@
           <t>1503495.0</t>
         </is>
       </c>
-      <c r="AX111" t="inlineStr">
-        <is>
-          <t>678112.6</t>
-        </is>
+      <c r="AX111" t="n">
+        <v>678112.6</v>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
           <t>861484.8</t>
         </is>
       </c>
-      <c r="AZ111" t="inlineStr">
-        <is>
-          <t>846536.22</t>
-        </is>
+      <c r="AZ111" t="n">
+        <v>846536.22</v>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
@@ -48666,8 +48004,10 @@
           <t>27331.93885502627</t>
         </is>
       </c>
-      <c r="BD111" t="n">
-        <v>1503495</v>
+      <c r="BD111" t="inlineStr">
+        <is>
+          <t>1503495.0</t>
+        </is>
       </c>
       <c r="BE111" t="inlineStr">
         <is>
@@ -48833,7 +48173,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -49017,15 +48357,11 @@
           <t>14.88</t>
         </is>
       </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="AN112" t="inlineStr">
-        <is>
-          <t>15.18</t>
-        </is>
+      <c r="AM112" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>15.18</v>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
@@ -49072,20 +48408,16 @@
           <t>4596917.0</t>
         </is>
       </c>
-      <c r="AX112" t="inlineStr">
-        <is>
-          <t>3279241.0</t>
-        </is>
+      <c r="AX112" t="n">
+        <v>3279241</v>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
           <t>4133860.2</t>
         </is>
       </c>
-      <c r="AZ112" t="inlineStr">
-        <is>
-          <t>3677240.78</t>
-        </is>
+      <c r="AZ112" t="n">
+        <v>3677240.78</v>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
@@ -49102,8 +48434,10 @@
           <t>98605.48098267242</t>
         </is>
       </c>
-      <c r="BD112" t="n">
-        <v>4596917</v>
+      <c r="BD112" t="inlineStr">
+        <is>
+          <t>4596917.0</t>
+        </is>
       </c>
       <c r="BE112" t="inlineStr">
         <is>
@@ -49269,7 +48603,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -49453,15 +48787,11 @@
           <t>14.86</t>
         </is>
       </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>15.01</t>
-        </is>
-      </c>
-      <c r="AN113" t="inlineStr">
-        <is>
-          <t>15.19</t>
-        </is>
+      <c r="AM113" t="n">
+        <v>15.01</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>15.19</v>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
@@ -49508,20 +48838,16 @@
           <t>3930958.0</t>
         </is>
       </c>
-      <c r="AX113" t="inlineStr">
-        <is>
-          <t>3128966.2</t>
-        </is>
+      <c r="AX113" t="n">
+        <v>3128966.2</v>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
           <t>4002896.9</t>
         </is>
       </c>
-      <c r="AZ113" t="inlineStr">
-        <is>
-          <t>3699799.16</t>
-        </is>
+      <c r="AZ113" t="n">
+        <v>3699799.16</v>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
@@ -49538,8 +48864,10 @@
           <t>28205.11676028185</t>
         </is>
       </c>
-      <c r="BD113" t="n">
-        <v>3930958</v>
+      <c r="BD113" t="inlineStr">
+        <is>
+          <t>3930958.0</t>
+        </is>
       </c>
       <c r="BE113" t="inlineStr">
         <is>
@@ -49705,7 +49033,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -49889,15 +49217,11 @@
           <t>14.87</t>
         </is>
       </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>15.02</t>
-        </is>
-      </c>
-      <c r="AN114" t="inlineStr">
-        <is>
-          <t>15.21</t>
-        </is>
+      <c r="AM114" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>15.21</v>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
@@ -49944,20 +49268,16 @@
           <t>3631237.0</t>
         </is>
       </c>
-      <c r="AX114" t="inlineStr">
-        <is>
-          <t>3449483.0</t>
-        </is>
+      <c r="AX114" t="n">
+        <v>3449483</v>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
           <t>3824303.2</t>
         </is>
       </c>
-      <c r="AZ114" t="inlineStr">
-        <is>
-          <t>3704134.96</t>
-        </is>
+      <c r="AZ114" t="n">
+        <v>3704134.96</v>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
@@ -49974,8 +49294,10 @@
           <t>-2021.407727429643</t>
         </is>
       </c>
-      <c r="BD114" t="n">
-        <v>3631237</v>
+      <c r="BD114" t="inlineStr">
+        <is>
+          <t>3631237.0</t>
+        </is>
       </c>
       <c r="BE114" t="inlineStr">
         <is>
@@ -50141,7 +49463,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -50325,15 +49647,11 @@
           <t>14.88</t>
         </is>
       </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>15.04</t>
-        </is>
-      </c>
-      <c r="AN115" t="inlineStr">
-        <is>
-          <t>15.22</t>
-        </is>
+      <c r="AM115" t="n">
+        <v>15.04</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>15.22</v>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
@@ -50380,20 +49698,16 @@
           <t>2826110.0</t>
         </is>
       </c>
-      <c r="AX115" t="inlineStr">
-        <is>
-          <t>4301019.6</t>
-        </is>
+      <c r="AX115" t="n">
+        <v>4301019.6</v>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
           <t>3630997.9</t>
         </is>
       </c>
-      <c r="AZ115" t="inlineStr">
-        <is>
-          <t>3705852.72</t>
-        </is>
+      <c r="AZ115" t="n">
+        <v>3705852.72</v>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
@@ -50410,8 +49724,10 @@
           <t>-13016.99957675207</t>
         </is>
       </c>
-      <c r="BD115" t="n">
-        <v>2826110</v>
+      <c r="BD115" t="inlineStr">
+        <is>
+          <t>2826110.0</t>
+        </is>
       </c>
       <c r="BE115" t="inlineStr">
         <is>
@@ -50577,7 +49893,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -50761,15 +50077,11 @@
           <t>14.92</t>
         </is>
       </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>15.06</t>
-        </is>
-      </c>
-      <c r="AN116" t="inlineStr">
-        <is>
-          <t>15.24</t>
-        </is>
+      <c r="AM116" t="n">
+        <v>15.06</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>15.24</v>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
@@ -50816,20 +50128,16 @@
           <t>1410983.0</t>
         </is>
       </c>
-      <c r="AX116" t="inlineStr">
-        <is>
-          <t>4162838.4</t>
-        </is>
+      <c r="AX116" t="n">
+        <v>4162838.4</v>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
           <t>3564716.2</t>
         </is>
       </c>
-      <c r="AZ116" t="inlineStr">
-        <is>
-          <t>3682123.92</t>
-        </is>
+      <c r="AZ116" t="n">
+        <v>3682123.92</v>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
@@ -50846,8 +50154,10 @@
           <t>58003.51205195673</t>
         </is>
       </c>
-      <c r="BD116" t="n">
-        <v>1410983</v>
+      <c r="BD116" t="inlineStr">
+        <is>
+          <t>1410983.0</t>
+        </is>
       </c>
       <c r="BE116" t="inlineStr">
         <is>
@@ -51013,7 +50323,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -51197,15 +50507,11 @@
           <t>14.96</t>
         </is>
       </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>15.08</t>
-        </is>
-      </c>
-      <c r="AN117" t="inlineStr">
-        <is>
-          <t>15.25</t>
-        </is>
+      <c r="AM117" t="n">
+        <v>15.08</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>15.25</v>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
@@ -51252,20 +50558,16 @@
           <t>3845543.0</t>
         </is>
       </c>
-      <c r="AX117" t="inlineStr">
-        <is>
-          <t>4988479.4</t>
-        </is>
+      <c r="AX117" t="n">
+        <v>4988479.4</v>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
           <t>3674459.9</t>
         </is>
       </c>
-      <c r="AZ117" t="inlineStr">
-        <is>
-          <t>3727140.3</t>
-        </is>
+      <c r="AZ117" t="n">
+        <v>3727140.3</v>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
@@ -51282,8 +50584,10 @@
           <t>309010.5818053996</t>
         </is>
       </c>
-      <c r="BD117" t="n">
-        <v>3845543</v>
+      <c r="BD117" t="inlineStr">
+        <is>
+          <t>3845543.0</t>
+        </is>
       </c>
       <c r="BE117" t="inlineStr">
         <is>
@@ -51449,7 +50753,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -51633,15 +50937,11 @@
           <t>15.02</t>
         </is>
       </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>15.1</t>
-        </is>
-      </c>
-      <c r="AN118" t="inlineStr">
-        <is>
-          <t>15.27</t>
-        </is>
+      <c r="AM118" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>15.27</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
@@ -51688,20 +50988,16 @@
           <t>5533542.0</t>
         </is>
       </c>
-      <c r="AX118" t="inlineStr">
-        <is>
-          <t>4876827.6</t>
-        </is>
+      <c r="AX118" t="n">
+        <v>4876827.6</v>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
           <t>3752350.7</t>
         </is>
       </c>
-      <c r="AZ118" t="inlineStr">
-        <is>
-          <t>3700419.8</t>
-        </is>
+      <c r="AZ118" t="n">
+        <v>3700419.8</v>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
@@ -51718,8 +51014,10 @@
           <t>395710.3035315536</t>
         </is>
       </c>
-      <c r="BD118" t="n">
-        <v>5533542</v>
+      <c r="BD118" t="inlineStr">
+        <is>
+          <t>5533542.0</t>
+        </is>
       </c>
       <c r="BE118" t="inlineStr">
         <is>
@@ -51885,7 +51183,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -52069,15 +51367,11 @@
           <t>15.05</t>
         </is>
       </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>15.11</t>
-        </is>
-      </c>
-      <c r="AN119" t="inlineStr">
-        <is>
-          <t>15.28</t>
-        </is>
+      <c r="AM119" t="n">
+        <v>15.11</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>15.28</v>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
@@ -52124,20 +51418,16 @@
           <t>7888920.0</t>
         </is>
       </c>
-      <c r="AX119" t="inlineStr">
-        <is>
-          <t>4199123.4</t>
-        </is>
+      <c r="AX119" t="n">
+        <v>4199123.4</v>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
           <t>3484214.2</t>
         </is>
       </c>
-      <c r="AZ119" t="inlineStr">
-        <is>
-          <t>3634499.9</t>
-        </is>
+      <c r="AZ119" t="n">
+        <v>3634499.9</v>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
@@ -52154,8 +51444,10 @@
           <t>324577.5022999323</t>
         </is>
       </c>
-      <c r="BD119" t="n">
-        <v>7888920</v>
+      <c r="BD119" t="inlineStr">
+        <is>
+          <t>7888920.0</t>
+        </is>
       </c>
       <c r="BE119" t="inlineStr">
         <is>
@@ -52321,7 +51613,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -52505,15 +51797,11 @@
           <t>15.07</t>
         </is>
       </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>15.12</t>
-        </is>
-      </c>
-      <c r="AN120" t="inlineStr">
-        <is>
-          <t>15.29</t>
-        </is>
+      <c r="AM120" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>15.29</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
@@ -52560,20 +51848,16 @@
           <t>2135204.0</t>
         </is>
       </c>
-      <c r="AX120" t="inlineStr">
-        <is>
-          <t>2960976.2</t>
-        </is>
+      <c r="AX120" t="n">
+        <v>2960976.2</v>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
           <t>2909465.0</t>
         </is>
       </c>
-      <c r="AZ120" t="inlineStr">
-        <is>
-          <t>3530066.62</t>
-        </is>
+      <c r="AZ120" t="n">
+        <v>3530066.62</v>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
@@ -52590,8 +51874,10 @@
           <t>-40994.76739880955</t>
         </is>
       </c>
-      <c r="BD120" t="n">
-        <v>2135204</v>
+      <c r="BD120" t="inlineStr">
+        <is>
+          <t>2135204.0</t>
+        </is>
       </c>
       <c r="BE120" t="inlineStr">
         <is>
@@ -52757,7 +52043,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -52941,15 +52227,11 @@
           <t>15.09</t>
         </is>
       </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>15.12</t>
-        </is>
-      </c>
-      <c r="AN121" t="inlineStr">
-        <is>
-          <t>15.3</t>
-        </is>
+      <c r="AM121" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>15.3</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
@@ -52996,20 +52278,16 @@
           <t>5539188.0</t>
         </is>
       </c>
-      <c r="AX121" t="inlineStr">
-        <is>
-          <t>2966594.0</t>
-        </is>
+      <c r="AX121" t="n">
+        <v>2966594</v>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
           <t>3042316.9</t>
         </is>
       </c>
-      <c r="AZ121" t="inlineStr">
-        <is>
-          <t>3551181.96</t>
-        </is>
+      <c r="AZ121" t="n">
+        <v>3551181.96</v>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
@@ -53026,8 +52304,10 @@
           <t>54692.80329580279</t>
         </is>
       </c>
-      <c r="BD121" t="n">
-        <v>5539188</v>
+      <c r="BD121" t="inlineStr">
+        <is>
+          <t>5539188.0</t>
+        </is>
       </c>
       <c r="BE121" t="inlineStr">
         <is>
@@ -53193,7 +52473,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -53377,15 +52657,11 @@
           <t>15.1</t>
         </is>
       </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>15.12</t>
-        </is>
-      </c>
-      <c r="AN122" t="inlineStr">
-        <is>
-          <t>15.31</t>
-        </is>
+      <c r="AM122" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>15.31</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
@@ -53432,20 +52708,16 @@
           <t>3287284.0</t>
         </is>
       </c>
-      <c r="AX122" t="inlineStr">
-        <is>
-          <t>2360440.4</t>
-        </is>
+      <c r="AX122" t="n">
+        <v>2360440.4</v>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
           <t>2852335.2</t>
         </is>
       </c>
-      <c r="AZ122" t="inlineStr">
-        <is>
-          <t>3481032.8</t>
-        </is>
+      <c r="AZ122" t="n">
+        <v>3481032.8</v>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
@@ -53462,8 +52734,10 @@
           <t>-175276.5529724583</t>
         </is>
       </c>
-      <c r="BD122" t="n">
-        <v>3287284</v>
+      <c r="BD122" t="inlineStr">
+        <is>
+          <t>3287284.0</t>
+        </is>
       </c>
       <c r="BE122" t="inlineStr">
         <is>
